--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/MISSOURI_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/MISSOURI_2021.xlsx
@@ -3750,7 +3750,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C189">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C194">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C461">
